--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>127013863</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013840</v>
+        <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505062</v>
+        <v>505033</v>
       </c>
       <c r="R8" t="n">
-        <v>7141290</v>
+        <v>7141160</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,11 +1448,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013869</v>
+        <v>127013840</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505033</v>
+        <v>505062</v>
       </c>
       <c r="R9" t="n">
-        <v>7141160</v>
+        <v>7141290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013874</v>
+        <v>127013838</v>
       </c>
       <c r="B14" t="n">
-        <v>91652</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,16 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505068</v>
+        <v>504949</v>
       </c>
       <c r="R14" t="n">
-        <v>7141288</v>
+        <v>7141369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,13 +2057,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2077,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013838</v>
+        <v>127013874</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>91726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,21 +2097,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504949</v>
+        <v>505068</v>
       </c>
       <c r="R15" t="n">
-        <v>7141369</v>
+        <v>7141288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,17 +2154,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>127013863</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>127013874</v>
       </c>
       <c r="B15" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013869</v>
+        <v>127013840</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505033</v>
+        <v>505062</v>
       </c>
       <c r="R8" t="n">
-        <v>7141160</v>
+        <v>7141290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,6 +1448,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013840</v>
+        <v>127013869</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505062</v>
+        <v>505033</v>
       </c>
       <c r="R9" t="n">
-        <v>7141290</v>
+        <v>7141160</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,11 +1550,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013838</v>
+        <v>127013874</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,21 +1995,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504949</v>
+        <v>505068</v>
       </c>
       <c r="R14" t="n">
-        <v>7141369</v>
+        <v>7141288</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,17 +2052,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013874</v>
+        <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>91732</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,16 +2088,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505068</v>
+        <v>504949</v>
       </c>
       <c r="R15" t="n">
-        <v>7141288</v>
+        <v>7141369</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,13 +2150,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1987,7 +1987,7 @@
         <v>127013874</v>
       </c>
       <c r="B14" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013840</v>
+        <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505062</v>
+        <v>505033</v>
       </c>
       <c r="R8" t="n">
-        <v>7141290</v>
+        <v>7141160</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,11 +1448,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013869</v>
+        <v>127013840</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505033</v>
+        <v>505062</v>
       </c>
       <c r="R9" t="n">
-        <v>7141160</v>
+        <v>7141290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1984,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013874</v>
+        <v>127013838</v>
       </c>
       <c r="B14" t="n">
-        <v>91733</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,16 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505068</v>
+        <v>504949</v>
       </c>
       <c r="R14" t="n">
-        <v>7141288</v>
+        <v>7141369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,13 +2057,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2077,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013838</v>
+        <v>127013874</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>91733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,21 +2097,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504949</v>
+        <v>505068</v>
       </c>
       <c r="R15" t="n">
-        <v>7141369</v>
+        <v>7141288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,17 +2154,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013840</v>
+        <v>127013874</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1485,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505062</v>
+        <v>505068</v>
       </c>
       <c r="R9" t="n">
-        <v>7141290</v>
+        <v>7141288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,17 +1542,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013837</v>
+        <v>127013840</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1611,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504909</v>
+        <v>505062</v>
       </c>
       <c r="R10" t="n">
-        <v>7141338</v>
+        <v>7141290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127013834</v>
+        <v>127013837</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1713,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504921</v>
+        <v>504909</v>
       </c>
       <c r="R11" t="n">
-        <v>7141196</v>
+        <v>7141338</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013841</v>
+        <v>127013834</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1815,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504923</v>
+        <v>504921</v>
       </c>
       <c r="R12" t="n">
-        <v>7141035</v>
+        <v>7141196</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1846,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013839</v>
+        <v>127013841</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1917,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505051</v>
+        <v>504923</v>
       </c>
       <c r="R13" t="n">
-        <v>7141297</v>
+        <v>7141035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013838</v>
+        <v>127013839</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -2019,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504949</v>
+        <v>505051</v>
       </c>
       <c r="R14" t="n">
-        <v>7141369</v>
+        <v>7141297</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2050,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013874</v>
+        <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>91733</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,16 +2088,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505068</v>
+        <v>504949</v>
       </c>
       <c r="R15" t="n">
-        <v>7141288</v>
+        <v>7141369</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,13 +2150,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>127013863</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>127013874</v>
       </c>
       <c r="B9" t="n">
-        <v>91733</v>
+        <v>91737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127013840</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127013837</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127013834</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>127013841</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127013839</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>127013863</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>127013874</v>
       </c>
       <c r="B9" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127013840</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127013837</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127013834</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>127013841</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127013839</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1570,7 +1570,7 @@
         <v>127013840</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127013837</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127013834</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>127013841</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127013839</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1570,7 +1570,7 @@
         <v>127013840</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127013837</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127013834</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>127013841</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127013839</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127013838</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33890-2025 artfynd.xlsx
+++ b/artfynd/A 33890-2025 artfynd.xlsx
@@ -1283,7 +1283,7 @@
         <v>127013863</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127013869</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013874</v>
+        <v>127013840</v>
       </c>
       <c r="B9" t="n">
-        <v>91739</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,16 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505068</v>
+        <v>505062</v>
       </c>
       <c r="R9" t="n">
-        <v>7141288</v>
+        <v>7141290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,13 +1547,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013840</v>
+        <v>127013837</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1602,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505062</v>
+        <v>504909</v>
       </c>
       <c r="R10" t="n">
-        <v>7141290</v>
+        <v>7141338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127013837</v>
+        <v>127013834</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1704,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504909</v>
+        <v>504921</v>
       </c>
       <c r="R11" t="n">
-        <v>7141338</v>
+        <v>7141196</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1753,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013834</v>
+        <v>127013841</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1806,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504921</v>
+        <v>504923</v>
       </c>
       <c r="R12" t="n">
-        <v>7141196</v>
+        <v>7141035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1855,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013841</v>
+        <v>127013839</v>
       </c>
       <c r="B13" t="n">
         <v>57672</v>
@@ -1908,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504923</v>
+        <v>505051</v>
       </c>
       <c r="R13" t="n">
-        <v>7141035</v>
+        <v>7141297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1957,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127013839</v>
+        <v>127013838</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -2010,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505051</v>
+        <v>504949</v>
       </c>
       <c r="R14" t="n">
-        <v>7141297</v>
+        <v>7141369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127013838</v>
+        <v>127013874</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>91726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,21 +2097,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504949</v>
+        <v>505068</v>
       </c>
       <c r="R15" t="n">
-        <v>7141369</v>
+        <v>7141288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,17 +2154,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
